--- a/artfynd/A 52808-2023 artfynd.xlsx
+++ b/artfynd/A 52808-2023 artfynd.xlsx
@@ -2908,7 +2908,7 @@
         <v>115608388</v>
       </c>
       <c r="B21" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>115608397</v>
       </c>
       <c r="B22" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 52808-2023 artfynd.xlsx
+++ b/artfynd/A 52808-2023 artfynd.xlsx
@@ -2908,7 +2908,7 @@
         <v>115608388</v>
       </c>
       <c r="B21" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>115608397</v>
       </c>
       <c r="B22" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 52808-2023 artfynd.xlsx
+++ b/artfynd/A 52808-2023 artfynd.xlsx
@@ -2908,7 +2908,7 @@
         <v>115608388</v>
       </c>
       <c r="B21" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>115608397</v>
       </c>
       <c r="B22" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 52808-2023 artfynd.xlsx
+++ b/artfynd/A 52808-2023 artfynd.xlsx
@@ -2908,7 +2908,7 @@
         <v>115608388</v>
       </c>
       <c r="B21" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>115608397</v>
       </c>
       <c r="B22" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 52808-2023 artfynd.xlsx
+++ b/artfynd/A 52808-2023 artfynd.xlsx
@@ -2908,7 +2908,7 @@
         <v>115608388</v>
       </c>
       <c r="B21" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>115608397</v>
       </c>
       <c r="B22" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 52808-2023 artfynd.xlsx
+++ b/artfynd/A 52808-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6193,6 +6193,633 @@
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126575708</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Penningsbergen, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>659007</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6671611</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Ella Perry</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Ella Perry</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126577835</v>
+      </c>
+      <c r="B50" t="n">
+        <v>100543</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Penningsbergen, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>658871</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6671473</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Ella Perry</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Ella Perry</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126575716</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Penningsbergen, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>659073</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6671514</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Ella Perry</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Ella Perry</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126583471</v>
+      </c>
+      <c r="B52" t="n">
+        <v>91245</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Penningsbergen, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>658854</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6671463</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Ella Perry</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Ella Perry</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>126575906</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Penningsbergen, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>659050</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6671740</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Ella Perry</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Ella Perry</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>126576281</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Penningsbergen, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>658850</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6671497</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Ella Perry</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Ella Perry</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52808-2023 artfynd.xlsx
+++ b/artfynd/A 52808-2023 artfynd.xlsx
@@ -6195,39 +6195,35 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126575708</v>
+        <v>126577835</v>
       </c>
       <c r="B49" t="n">
-        <v>98361</v>
+        <v>100618</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -6238,10 +6234,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>659007</v>
+        <v>658871</v>
       </c>
       <c r="R49" t="n">
-        <v>6671611</v>
+        <v>6671473</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6301,35 +6297,39 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126577835</v>
+        <v>126575708</v>
       </c>
       <c r="B50" t="n">
-        <v>100543</v>
+        <v>98436</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>658871</v>
+        <v>659007</v>
       </c>
       <c r="R50" t="n">
-        <v>6671473</v>
+        <v>6671611</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6406,7 +6406,7 @@
         <v>126575716</v>
       </c>
       <c r="B51" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>126583471</v>
       </c>
       <c r="B52" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6610,10 +6610,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126576281</v>
+        <v>126575906</v>
       </c>
       <c r="B53" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>658850</v>
+        <v>659050</v>
       </c>
       <c r="R53" t="n">
-        <v>6671497</v>
+        <v>6671740</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6683,12 +6683,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6716,10 +6716,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126575906</v>
+        <v>126576281</v>
       </c>
       <c r="B54" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>659050</v>
+        <v>658850</v>
       </c>
       <c r="R54" t="n">
-        <v>6671740</v>
+        <v>6671497</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6789,12 +6789,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6825,7 +6825,7 @@
         <v>126645723</v>
       </c>
       <c r="B55" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 52808-2023 artfynd.xlsx
+++ b/artfynd/A 52808-2023 artfynd.xlsx
@@ -6198,7 +6198,7 @@
         <v>126577835</v>
       </c>
       <c r="B49" t="n">
-        <v>100618</v>
+        <v>100624</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>126575708</v>
       </c>
       <c r="B50" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>126575716</v>
       </c>
       <c r="B51" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>126583471</v>
       </c>
       <c r="B52" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6610,10 +6610,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126575906</v>
+        <v>126576281</v>
       </c>
       <c r="B53" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>659050</v>
+        <v>658850</v>
       </c>
       <c r="R53" t="n">
-        <v>6671740</v>
+        <v>6671497</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6683,12 +6683,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6716,10 +6716,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126576281</v>
+        <v>126575906</v>
       </c>
       <c r="B54" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>658850</v>
+        <v>659050</v>
       </c>
       <c r="R54" t="n">
-        <v>6671497</v>
+        <v>6671740</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6789,12 +6789,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6825,7 +6825,7 @@
         <v>126645723</v>
       </c>
       <c r="B55" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 52808-2023 artfynd.xlsx
+++ b/artfynd/A 52808-2023 artfynd.xlsx
@@ -6195,35 +6195,39 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126577835</v>
+        <v>126575708</v>
       </c>
       <c r="B49" t="n">
-        <v>100624</v>
+        <v>98442</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -6234,10 +6238,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>658871</v>
+        <v>659007</v>
       </c>
       <c r="R49" t="n">
-        <v>6671473</v>
+        <v>6671611</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6297,39 +6301,35 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126575708</v>
+        <v>126577835</v>
       </c>
       <c r="B50" t="n">
-        <v>98442</v>
+        <v>100624</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>659007</v>
+        <v>658871</v>
       </c>
       <c r="R50" t="n">
-        <v>6671611</v>
+        <v>6671473</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6610,7 +6610,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126576281</v>
+        <v>126575906</v>
       </c>
       <c r="B53" t="n">
         <v>98442</v>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J53" t="inlineStr"/>
@@ -6653,10 +6653,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>658850</v>
+        <v>659050</v>
       </c>
       <c r="R53" t="n">
-        <v>6671497</v>
+        <v>6671740</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6683,12 +6683,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6716,7 +6716,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126575906</v>
+        <v>126576281</v>
       </c>
       <c r="B54" t="n">
         <v>98442</v>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J54" t="inlineStr"/>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>659050</v>
+        <v>658850</v>
       </c>
       <c r="R54" t="n">
-        <v>6671740</v>
+        <v>6671497</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6789,12 +6789,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 52808-2023 artfynd.xlsx
+++ b/artfynd/A 52808-2023 artfynd.xlsx
@@ -6825,7 +6825,7 @@
         <v>126645723</v>
       </c>
       <c r="B55" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 52808-2023 artfynd.xlsx
+++ b/artfynd/A 52808-2023 artfynd.xlsx
@@ -909,12 +909,7 @@
         <v>115608419</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 52808-2023 artfynd.xlsx
+++ b/artfynd/A 52808-2023 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>115608419</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52808-2023 artfynd.xlsx
+++ b/artfynd/A 52808-2023 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>115608419</v>
       </c>
       <c r="B4" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52808-2023 artfynd.xlsx
+++ b/artfynd/A 52808-2023 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>115608419</v>
       </c>
       <c r="B4" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52808-2023 artfynd.xlsx
+++ b/artfynd/A 52808-2023 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>115608419</v>
       </c>
       <c r="B4" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52808-2023 artfynd.xlsx
+++ b/artfynd/A 52808-2023 artfynd.xlsx
@@ -909,7 +909,7 @@
         <v>115608419</v>
       </c>
       <c r="B4" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 52808-2023 artfynd.xlsx
+++ b/artfynd/A 52808-2023 artfynd.xlsx
@@ -6190,39 +6190,35 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126575708</v>
+        <v>126577835</v>
       </c>
       <c r="B49" t="n">
-        <v>98442</v>
+        <v>100618</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -6233,10 +6229,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>659007</v>
+        <v>658871</v>
       </c>
       <c r="R49" t="n">
-        <v>6671611</v>
+        <v>6671473</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6296,35 +6292,39 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126577835</v>
+        <v>126575708</v>
       </c>
       <c r="B50" t="n">
-        <v>100624</v>
+        <v>98436</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
@@ -6335,10 +6335,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>658871</v>
+        <v>659007</v>
       </c>
       <c r="R50" t="n">
-        <v>6671473</v>
+        <v>6671611</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6401,7 +6401,7 @@
         <v>126575716</v>
       </c>
       <c r="B51" t="n">
-        <v>98442</v>
+        <v>98436</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>126583471</v>
       </c>
       <c r="B52" t="n">
-        <v>91325</v>
+        <v>91319</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>126575906</v>
       </c>
       <c r="B53" t="n">
-        <v>98442</v>
+        <v>98436</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>126576281</v>
       </c>
       <c r="B54" t="n">
-        <v>98442</v>
+        <v>98436</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>126645723</v>
       </c>
       <c r="B55" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>

--- a/artfynd/A 52808-2023 artfynd.xlsx
+++ b/artfynd/A 52808-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115608553</v>
+        <v>115608450</v>
       </c>
       <c r="B2" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söderbotten, Upl</t>
+          <t>Penningbergen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>658764</v>
+        <v>658881</v>
       </c>
       <c r="R2" t="n">
-        <v>6671477</v>
+        <v>6671456</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115608458</v>
+        <v>115608451</v>
       </c>
       <c r="B3" t="n">
-        <v>90951</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>658756</v>
+        <v>658762</v>
       </c>
       <c r="R3" t="n">
-        <v>6671617</v>
+        <v>6671465</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -869,7 +858,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +868,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115608419</v>
+        <v>126583471</v>
       </c>
       <c r="B4" t="n">
-        <v>57717</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,49 +906,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Harparbottnen, Upl</t>
+          <t>Penningsbergen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>658944</v>
+        <v>658854</v>
       </c>
       <c r="R4" t="n">
-        <v>6671624</v>
+        <v>6671463</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,22 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:53</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:53</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,69 +977,56 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Ella Perry</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Ella Perry</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115608529</v>
+        <v>115608452</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1077,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>658792</v>
+        <v>658897</v>
       </c>
       <c r="R5" t="n">
-        <v>6671477</v>
+        <v>6671566</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1112,7 +1069,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1079,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,47 +1106,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115608530</v>
+        <v>115608458</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1197,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>658876</v>
+        <v>658756</v>
       </c>
       <c r="R6" t="n">
-        <v>6671606</v>
+        <v>6671617</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1232,7 +1179,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1189,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,62 +1216,60 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115602558</v>
+        <v>115608419</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Harparbottnen (Harparbottnen), Upl</t>
+          <t>Harparbottnen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>658969</v>
+        <v>658944</v>
       </c>
       <c r="R7" t="n">
-        <v>6671768</v>
+        <v>6671624</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1351,9 +1296,19 @@
           <t>2024-04-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,27 +1323,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115608563</v>
+        <v>115608421</v>
       </c>
       <c r="B8" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,27 +1346,35 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1424,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>658747</v>
+        <v>658857</v>
       </c>
       <c r="R8" t="n">
-        <v>6671574</v>
+        <v>6671582</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1459,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,15 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115608544</v>
+        <v>115608426</v>
       </c>
       <c r="B9" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,38 +1465,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Penningbergen, Upl</t>
+          <t>Söderbotten, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>658975</v>
+        <v>658734</v>
       </c>
       <c r="R9" t="n">
-        <v>6671180</v>
+        <v>6671627</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1575,7 +1536,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1585,7 +1546,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,15 +1573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115608564</v>
+        <v>115608427</v>
       </c>
       <c r="B10" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1628,27 +1584,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1656,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>658726</v>
+        <v>658746</v>
       </c>
       <c r="R10" t="n">
-        <v>6671586</v>
+        <v>6671590</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1691,7 +1655,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1665,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,53 +1692,60 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115604013</v>
+        <v>115608388</v>
       </c>
       <c r="B11" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Linbotten (Linbotten), Upl</t>
+          <t>Penningbergen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>658917</v>
+        <v>658873</v>
       </c>
       <c r="R11" t="n">
-        <v>6671824</v>
+        <v>6671493</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1801,16 +1772,26 @@
           <t>2024-04-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-04-01</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11" t="b">
         <v>0</v>
@@ -1818,55 +1799,58 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115608557</v>
+        <v>115608397</v>
       </c>
       <c r="B12" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1874,10 +1858,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>658747</v>
+        <v>658809</v>
       </c>
       <c r="R12" t="n">
-        <v>6671642</v>
+        <v>6671516</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1909,7 +1893,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,14 +1903,14 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" t="b">
         <v>0</v>
@@ -1946,62 +1930,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115608534</v>
+        <v>115608380</v>
       </c>
       <c r="B13" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Söderbotten, Upl</t>
+          <t>Penningbergen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>658670</v>
+        <v>658942</v>
       </c>
       <c r="R13" t="n">
-        <v>6671589</v>
+        <v>6671211</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2033,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2043,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2070,65 +2049,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115608426</v>
+        <v>115600453</v>
       </c>
       <c r="B14" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Söderbotten, Upl</t>
+          <t>Harparbottnen, Harparbottnen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>658734</v>
+        <v>659003</v>
       </c>
       <c r="R14" t="n">
-        <v>6671627</v>
+        <v>6671580</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2155,19 +2126,9 @@
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>17:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2182,69 +2143,69 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115608565</v>
+        <v>115602425</v>
       </c>
       <c r="B15" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Söderbotten, Upl</t>
+          <t>Linbotten, Linbotten, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>658677</v>
+        <v>658949</v>
       </c>
       <c r="R15" t="n">
-        <v>6671597</v>
+        <v>6671791</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2271,19 +2232,9 @@
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>17:46</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>17:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2298,27 +2249,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115604752</v>
+        <v>115602558</v>
       </c>
       <c r="B16" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,7 +2291,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2355,14 +2301,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Harparbottnen (Harparbottnen), Upl</t>
+          <t>Harparbottnen, Harparbottnen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>658974</v>
+        <v>658969</v>
       </c>
       <c r="R16" t="n">
-        <v>6671793</v>
+        <v>6671768</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2421,15 +2367,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115608503</v>
+        <v>115602642</v>
       </c>
       <c r="B17" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2456,26 +2397,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Harparbottnen, Upl</t>
+          <t>Harparbottnen, Harparbottnen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>659009</v>
+        <v>658985</v>
       </c>
       <c r="R17" t="n">
-        <v>6671580</v>
+        <v>6671754</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2502,19 +2444,9 @@
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:28</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2529,77 +2461,69 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115608421</v>
+        <v>115602766</v>
       </c>
       <c r="B18" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Söderbotten, Upl</t>
+          <t>Harparbottnen, Harparbottnen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>658857</v>
+        <v>658969</v>
       </c>
       <c r="R18" t="n">
-        <v>6671582</v>
+        <v>6671689</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2626,19 +2550,9 @@
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:50</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2653,27 +2567,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115605954</v>
+        <v>115604752</v>
       </c>
       <c r="B19" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2609,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2710,14 +2619,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Harparbottnen (Harparbottnen), Upl</t>
+          <t>Harparbottnen, Harparbottnen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>659059</v>
+        <v>658974</v>
       </c>
       <c r="R19" t="n">
-        <v>6671758</v>
+        <v>6671793</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2776,15 +2685,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115608511</v>
+        <v>115605153</v>
       </c>
       <c r="B20" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2715,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2819,22 +2723,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Harparbottnen, Upl</t>
+          <t>Harparbottnen, Harparbottnen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>658997</v>
+        <v>659071</v>
       </c>
       <c r="R20" t="n">
-        <v>6671598</v>
+        <v>6671703</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2861,19 +2762,9 @@
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2888,77 +2779,69 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115608388</v>
+        <v>115605564</v>
       </c>
       <c r="B21" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Penningbergen, Upl</t>
+          <t>Harparbottnen, Harparbottnen, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>658873</v>
+        <v>659038</v>
       </c>
       <c r="R21" t="n">
-        <v>6671493</v>
+        <v>6671803</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2985,26 +2868,16 @@
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>16:11</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>16:11</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="b">
         <v>0</v>
@@ -3012,77 +2885,69 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115608397</v>
+        <v>115605954</v>
       </c>
       <c r="B22" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Söderbotten, Upl</t>
+          <t>Harparbottnen, Harparbottnen, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>658809</v>
+        <v>659059</v>
       </c>
       <c r="R22" t="n">
-        <v>6671516</v>
+        <v>6671758</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3109,26 +2974,16 @@
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:25</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="b">
         <v>0</v>
@@ -3136,69 +2991,69 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115608550</v>
+        <v>115606888</v>
       </c>
       <c r="B23" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Söderbotten, Upl</t>
+          <t>Harparbottnen, Harparbottnen, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>658898</v>
+        <v>659097</v>
       </c>
       <c r="R23" t="n">
-        <v>6671558</v>
+        <v>6671740</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3225,19 +3080,9 @@
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:08</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3252,27 +3097,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115608527</v>
+        <v>115607066</v>
       </c>
       <c r="B24" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3299,7 +3139,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3307,22 +3147,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Söderbotten, Upl</t>
+          <t>Harparbottnen, Harparbottnen, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>658798</v>
+        <v>659067</v>
       </c>
       <c r="R24" t="n">
-        <v>6671484</v>
+        <v>6671713</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3349,19 +3186,9 @@
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>16:23</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>16:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3376,27 +3203,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115608517</v>
+        <v>115608503</v>
       </c>
       <c r="B25" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3423,27 +3245,23 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Söderbotten, Upl</t>
+          <t>Harparbottnen, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>658891</v>
+        <v>659009</v>
       </c>
       <c r="R25" t="n">
-        <v>6671542</v>
+        <v>6671580</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3475,7 +3293,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3485,12 +3303,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:07</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Räknade en och en, finns säkert ännu fler, många är fortfarande hårt tryckta mot marken efter snön.</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3517,53 +3330,60 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115603366</v>
+        <v>115608511</v>
       </c>
       <c r="B26" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Linbotten (Linbotten), Upl</t>
+          <t>Harparbottnen, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>658880</v>
+        <v>658997</v>
       </c>
       <c r="R26" t="n">
-        <v>6671803</v>
+        <v>6671598</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3590,9 +3410,19 @@
           <t>2024-04-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3607,27 +3437,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115600453</v>
+        <v>115608514</v>
       </c>
       <c r="B27" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3654,7 +3479,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3662,19 +3487,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Harparbottnen (Harparbottnen), Upl</t>
+          <t>Harparbottnen, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
         <v>659003</v>
       </c>
       <c r="R27" t="n">
-        <v>6671580</v>
+        <v>6671605</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3701,9 +3529,19 @@
           <t>2024-04-01</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3718,27 +3556,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115607066</v>
+        <v>115608517</v>
       </c>
       <c r="B28" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3765,7 +3598,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3773,19 +3606,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Harparbottnen (Harparbottnen), Upl</t>
+          <t>Söderbotten, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>659067</v>
+        <v>658891</v>
       </c>
       <c r="R28" t="n">
-        <v>6671713</v>
+        <v>6671542</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3812,9 +3648,24 @@
           <t>2024-04-01</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Räknade en och en, finns säkert ännu fler, många är fortfarande hårt tryckta mot marken efter snön.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3829,53 +3680,56 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115608552</v>
+        <v>115608523</v>
       </c>
       <c r="B29" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -3888,7 +3742,7 @@
         <v>658801</v>
       </c>
       <c r="R29" t="n">
-        <v>6671467</v>
+        <v>6671465</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3920,7 +3774,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3930,7 +3784,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3957,15 +3811,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115608523</v>
+        <v>115608527</v>
       </c>
       <c r="B30" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3992,7 +3841,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4009,10 +3858,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>658801</v>
+        <v>658798</v>
       </c>
       <c r="R30" t="n">
-        <v>6671465</v>
+        <v>6671484</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4044,7 +3893,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4054,7 +3903,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4081,54 +3930,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>115608467</v>
+        <v>115608528</v>
       </c>
       <c r="B31" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Harparbottnen, Upl</t>
+          <t>Söderbotten, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>658933</v>
+        <v>658791</v>
       </c>
       <c r="R31" t="n">
-        <v>6671624</v>
+        <v>6671464</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4160,7 +4012,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4170,7 +4022,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4197,15 +4049,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115605564</v>
+        <v>115608529</v>
       </c>
       <c r="B32" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4232,7 +4079,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4240,19 +4087,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Harparbottnen (Harparbottnen), Upl</t>
+          <t>Söderbotten, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>659038</v>
+        <v>658792</v>
       </c>
       <c r="R32" t="n">
-        <v>6671803</v>
+        <v>6671477</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4279,9 +4129,19 @@
           <t>2024-04-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4296,27 +4156,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115608538</v>
+        <v>115608530</v>
       </c>
       <c r="B33" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4343,14 +4198,10 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -4360,10 +4211,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>658810</v>
+        <v>658876</v>
       </c>
       <c r="R33" t="n">
-        <v>6671722</v>
+        <v>6671606</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4395,7 +4246,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4405,7 +4256,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4432,54 +4283,57 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115608549</v>
+        <v>115608532</v>
       </c>
       <c r="B34" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Harparbottnen, Upl</t>
+          <t>Söderbotten, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>658977</v>
+        <v>658740</v>
       </c>
       <c r="R34" t="n">
-        <v>6671596</v>
+        <v>6671626</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4511,7 +4365,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4521,7 +4375,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4548,51 +4402,46 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>115608427</v>
+        <v>115608534</v>
       </c>
       <c r="B35" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4600,10 +4449,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>658746</v>
+        <v>658670</v>
       </c>
       <c r="R35" t="n">
-        <v>6671590</v>
+        <v>6671589</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4635,7 +4484,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4645,7 +4494,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4672,15 +4521,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>115602425</v>
+        <v>115608538</v>
       </c>
       <c r="B36" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4707,7 +4551,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4715,19 +4559,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Linbotten (Linbotten), Upl</t>
+          <t>Söderbotten, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>658949</v>
+        <v>658810</v>
       </c>
       <c r="R36" t="n">
-        <v>6671791</v>
+        <v>6671722</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4754,9 +4601,19 @@
           <t>2024-04-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4771,27 +4628,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>115608532</v>
+        <v>115608540</v>
       </c>
       <c r="B37" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4818,7 +4670,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4835,10 +4687,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>658740</v>
+        <v>658838</v>
       </c>
       <c r="R37" t="n">
-        <v>6671626</v>
+        <v>6671707</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -4870,7 +4722,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4880,7 +4732,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4907,57 +4759,56 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>115608554</v>
+        <v>126513254</v>
       </c>
       <c r="B38" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Söderbotten, Upl</t>
+          <t>Penningsbergen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>658788</v>
+        <v>658887</v>
       </c>
       <c r="R38" t="n">
-        <v>6671498</v>
+        <v>6671734</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4981,22 +4832,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>16:45</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>16:45</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5005,33 +4846,29 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Ella Perry</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Ella Perry</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>115606888</v>
+        <v>126514782</v>
       </c>
       <c r="B39" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5061,21 +4898,20 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Harparbottnen (Harparbottnen), Upl</t>
+          <t>Penningsbergen, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>659097</v>
+        <v>659034</v>
       </c>
       <c r="R39" t="n">
-        <v>6671740</v>
+        <v>6671618</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5102,12 +4938,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5116,75 +4952,75 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ella Perry</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ella Perry</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>115608468</v>
+        <v>126575708</v>
       </c>
       <c r="B40" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Söderbotten, Upl</t>
+          <t>Penningsbergen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>658795</v>
+        <v>659007</v>
       </c>
       <c r="R40" t="n">
-        <v>6671471</v>
+        <v>6671611</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5208,22 +5044,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>16:20</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>16:20</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5232,83 +5058,75 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Ella Perry</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Ella Perry</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>115608380</v>
+        <v>126575716</v>
       </c>
       <c r="B41" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Penningbergen, Upl</t>
+          <t>Penningsbergen, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>658942</v>
+        <v>659073</v>
       </c>
       <c r="R41" t="n">
-        <v>6671211</v>
+        <v>6671514</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5332,22 +5150,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:56</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5356,68 +5164,72 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Ella Perry</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Ella Perry</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>115600755</v>
+        <v>126575906</v>
       </c>
       <c r="B42" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Harparbottnen (Harparbottnen), Upl</t>
+          <t>Penningsbergen, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>659025</v>
+        <v>659050</v>
       </c>
       <c r="R42" t="n">
-        <v>6671550</v>
+        <v>6671740</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5444,12 +5256,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5458,33 +5270,29 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ella Perry</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ella Perry</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>115605153</v>
+        <v>126576281</v>
       </c>
       <c r="B43" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5511,24 +5319,23 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Harparbottnen (Harparbottnen), Upl</t>
+          <t>Penningsbergen, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>659071</v>
+        <v>658850</v>
       </c>
       <c r="R43" t="n">
-        <v>6671703</v>
+        <v>6671497</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5555,12 +5362,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5569,33 +5376,29 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ella Perry</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ella Perry</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>115608514</v>
+        <v>126645723</v>
       </c>
       <c r="B44" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5622,30 +5425,26 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Harparbottnen, Upl</t>
+          <t>Penningsbergen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>659003</v>
+        <v>658693</v>
       </c>
       <c r="R44" t="n">
-        <v>6671605</v>
+        <v>6671618</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5669,22 +5468,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5693,83 +5482,67 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Ella Perry</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Ella Perry</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>115608540</v>
+        <v>115600755</v>
       </c>
       <c r="B45" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Söderbotten, Upl</t>
+          <t>Harparbottnen, Harparbottnen, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>658838</v>
+        <v>659025</v>
       </c>
       <c r="R45" t="n">
-        <v>6671707</v>
+        <v>6671550</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5796,19 +5569,9 @@
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>18:09</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>18:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5823,68 +5586,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>115608450</v>
+        <v>115603366</v>
       </c>
       <c r="B46" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Penningbergen, Upl</t>
+          <t>Linbotten, Linbotten, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>658881</v>
+        <v>658880</v>
       </c>
       <c r="R46" t="n">
-        <v>6671456</v>
+        <v>6671803</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5911,19 +5666,9 @@
           <t>2024-04-01</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>15:10</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-04-01</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>15:10</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5938,74 +5683,61 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>115608528</v>
+        <v>115608467</v>
       </c>
       <c r="B47" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Söderbotten, Upl</t>
+          <t>Harparbottnen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>658791</v>
+        <v>658933</v>
       </c>
       <c r="R47" t="n">
-        <v>6671464</v>
+        <v>6671624</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6037,7 +5769,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6047,7 +5779,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6074,15 +5806,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>115608560</v>
+        <v>115608468</v>
       </c>
       <c r="B48" t="n">
-        <v>99909</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6090,21 +5817,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6118,10 +5845,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>658734</v>
+        <v>658795</v>
       </c>
       <c r="R48" t="n">
-        <v>6671622</v>
+        <v>6671471</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6153,7 +5880,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6163,7 +5890,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6190,56 +5917,52 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126575708</v>
+        <v>115608469</v>
       </c>
       <c r="B49" t="n">
-        <v>98442</v>
+        <v>97983</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Penningsbergen, Upl</t>
+          <t>Linbotten, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>659007</v>
+        <v>658876</v>
       </c>
       <c r="R49" t="n">
-        <v>6671611</v>
+        <v>6671736</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6263,12 +5986,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6277,29 +6010,28 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ella Perry</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ella Perry</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126577835</v>
+        <v>115608471</v>
       </c>
       <c r="B50" t="n">
-        <v>100624</v>
+        <v>97983</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6307,21 +6039,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6331,17 +6063,17 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Penningsbergen, Upl</t>
+          <t>Söderbotten, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>658871</v>
+        <v>658787</v>
       </c>
       <c r="R50" t="n">
-        <v>6671473</v>
+        <v>6671723</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6365,12 +6097,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6379,72 +6121,63 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ella Perry</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ella Perry</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126575716</v>
+        <v>115604013</v>
       </c>
       <c r="B51" t="n">
-        <v>98442</v>
+        <v>101326</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Penningsbergen, Upl</t>
+          <t>Linbotten, Linbotten, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>659073</v>
+        <v>658917</v>
       </c>
       <c r="R51" t="n">
-        <v>6671514</v>
+        <v>6671824</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6471,12 +6204,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6485,70 +6218,70 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ella Perry</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ella Perry</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126583471</v>
+        <v>115608544</v>
       </c>
       <c r="B52" t="n">
-        <v>91325</v>
+        <v>101326</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Penningsbergen, Upl</t>
+          <t>Penningbergen, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>658854</v>
+        <v>658975</v>
       </c>
       <c r="R52" t="n">
-        <v>6671463</v>
+        <v>6671180</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6572,12 +6305,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6586,75 +6329,70 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Ella Perry</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Ella Perry</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126575906</v>
+        <v>115608549</v>
       </c>
       <c r="B53" t="n">
-        <v>98442</v>
+        <v>101326</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Penningsbergen, Upl</t>
+          <t>Harparbottnen, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>659050</v>
+        <v>658977</v>
       </c>
       <c r="R53" t="n">
-        <v>6671740</v>
+        <v>6671596</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6678,12 +6416,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6692,75 +6440,70 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Ella Perry</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Ella Perry</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126576281</v>
+        <v>115608550</v>
       </c>
       <c r="B54" t="n">
-        <v>98442</v>
+        <v>101326</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Penningsbergen, Upl</t>
+          <t>Söderbotten, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>658850</v>
+        <v>658898</v>
       </c>
       <c r="R54" t="n">
-        <v>6671497</v>
+        <v>6671558</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6784,12 +6527,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6798,75 +6551,70 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ella Perry</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ella Perry</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126645723</v>
+        <v>115608552</v>
       </c>
       <c r="B55" t="n">
-        <v>98443</v>
+        <v>101326</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Penningsbergen, Upl</t>
+          <t>Söderbotten, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>658693</v>
+        <v>658801</v>
       </c>
       <c r="R55" t="n">
-        <v>6671618</v>
+        <v>6671467</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6890,12 +6638,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6904,22 +6662,1011 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>115608553</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Söderbotten, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>658764</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6671477</v>
+      </c>
+      <c r="S56" t="n">
+        <v>4</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>115608554</v>
+      </c>
+      <c r="B57" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Söderbotten, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>658788</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6671498</v>
+      </c>
+      <c r="S57" t="n">
+        <v>4</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>115608555</v>
+      </c>
+      <c r="B58" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Linbotten, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>658876</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6671736</v>
+      </c>
+      <c r="S58" t="n">
+        <v>4</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>115608557</v>
+      </c>
+      <c r="B59" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Söderbotten, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>658747</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6671642</v>
+      </c>
+      <c r="S59" t="n">
+        <v>4</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>17:26</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>115608560</v>
+      </c>
+      <c r="B60" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Söderbotten, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>658734</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6671622</v>
+      </c>
+      <c r="S60" t="n">
+        <v>4</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>115608563</v>
+      </c>
+      <c r="B61" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Söderbotten, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>658747</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6671574</v>
+      </c>
+      <c r="S61" t="n">
+        <v>4</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>115608564</v>
+      </c>
+      <c r="B62" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Söderbotten, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>658726</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6671586</v>
+      </c>
+      <c r="S62" t="n">
+        <v>4</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>115608565</v>
+      </c>
+      <c r="B63" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Söderbotten, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>658677</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6671597</v>
+      </c>
+      <c r="S63" t="n">
+        <v>4</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126577835</v>
+      </c>
+      <c r="B64" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Penningsbergen, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>658871</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6671473</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Morkarla</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
           <t>Ella Perry</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
+      <c r="AX64" t="inlineStr">
         <is>
           <t>Ella Perry</t>
         </is>
       </c>
-      <c r="AY55" t="inlineStr"/>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52808-2023 artfynd.xlsx
+++ b/artfynd/A 52808-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY64"/>
+  <dimension ref="A1:AZ64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608450</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608451</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583471</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608452</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1213,6 +1238,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608458</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608419</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1451,6 +1486,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608421</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1570,6 +1610,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608426</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1689,6 +1734,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608427</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1808,6 +1858,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608388</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1927,6 +1982,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608397</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2046,6 +2106,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608380</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2152,6 +2217,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115600453</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2258,6 +2328,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115602425</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2364,6 +2439,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115602558</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2470,6 +2550,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115602642</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2576,6 +2661,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115602766</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2682,6 +2772,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115604752</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2788,6 +2883,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115605153</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2894,6 +2994,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115605564</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3000,6 +3105,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115605954</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3106,6 +3216,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115606888</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3212,6 +3327,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115607066</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3327,6 +3447,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608503</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3446,6 +3571,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608511</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3565,6 +3695,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608514</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3689,6 +3824,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608517</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3808,6 +3948,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608523</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3927,6 +4072,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608527</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4046,6 +4196,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608528</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4165,6 +4320,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608529</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4280,6 +4440,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608530</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4399,6 +4564,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608532</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4518,6 +4688,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608534</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4637,6 +4812,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608538</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4756,6 +4936,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608540</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4862,6 +5047,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126513254</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4968,6 +5158,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126514782</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5074,6 +5269,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126575708</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5180,6 +5380,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126575716</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5286,6 +5491,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126575906</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5392,6 +5602,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126576281</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5498,6 +5713,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126645723</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5595,6 +5815,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115600755</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5692,6 +5917,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115603366</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5803,6 +6033,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608467</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5914,6 +6149,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608468</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6025,6 +6265,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608469</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6136,6 +6381,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608471</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6233,6 +6483,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115604013</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6344,6 +6599,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608544</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6455,6 +6715,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608549</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6566,6 +6831,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608550</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6677,6 +6947,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608552</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6788,6 +7063,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608553</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6899,6 +7179,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608554</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7010,6 +7295,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608555</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7121,6 +7411,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608557</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7232,6 +7527,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608560</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7343,6 +7643,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608563</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7454,6 +7759,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608564</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7565,6 +7875,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115608565</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7667,8 +7982,78 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126577835</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>